--- a/tools/importer/reports/import-stores.report.xlsx
+++ b/tools/importer/reports/import-stores.report.xlsx
@@ -112,7 +112,7 @@
     <t>stores</t>
   </si>
   <si>
-    <t>2026-09-14T18:28:16.231Z</t>
+    <t>2026-09-14T19:17:38.844Z</t>
   </si>
   <si>
     <t>Get inspired to mix it up a little with 7UP! | 7up.com</t>
